--- a/sim/resources/sample/CasinoList.xlsx
+++ b/sim/resources/sample/CasinoList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="CasinoList" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -55,12 +55,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="F3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+场景中可同时容纳人数上限</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
@@ -71,7 +93,13 @@
     <t>城市名称</t>
   </si>
   <si>
-    <t>解锁条件</t>
+    <t>解锁条件1</t>
+  </si>
+  <si>
+    <t>解锁条件2</t>
+  </si>
+  <si>
+    <t>容纳人数上限</t>
   </si>
   <si>
     <t>int</t>
@@ -89,6 +117,9 @@
     <t>condition</t>
   </si>
   <si>
+    <t>CapacityNum</t>
+  </si>
+  <si>
     <t>拉斯维加斯</t>
   </si>
   <si>
@@ -101,25 +132,25 @@
     <t>云顶赌场</t>
   </si>
   <si>
-    <t>1002_999</t>
+    <t>1001_999;1002_999</t>
   </si>
   <si>
     <t>滨海赌场</t>
   </si>
   <si>
-    <t>1003_999</t>
+    <t>1002_999;1003_999</t>
   </si>
   <si>
     <t>亚特兰蒂斯</t>
   </si>
   <si>
-    <t>1004_999</t>
+    <t>1003_999;1004_999</t>
   </si>
   <si>
     <t>巴登赌场</t>
   </si>
   <si>
-    <t>1005_999</t>
+    <t>1004_999;1005_999</t>
   </si>
 </sst>
 </file>
@@ -310,12 +341,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1104,18 +1135,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFC10"/>
+  <dimension ref="A1:XFD10"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
     <col min="2" max="2" width="11.625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.7583333333333" style="2" customWidth="1"/>
-    <col min="5" max="16376" width="15.625" style="2" customWidth="1"/>
-    <col min="16377" max="16383" width="15.625" style="2"/>
+    <col min="3" max="4" width="15.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="41.6083333333333" style="2" customWidth="1"/>
+    <col min="6" max="16377" width="15.625" style="2" customWidth="1"/>
+    <col min="16378" max="16384" width="15.625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:1024 1025:16383">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:1024 1025:16384">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1125,11 +1156,15 @@
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
@@ -17507,20 +17542,23 @@
       <c r="XFA1" s="4"/>
       <c r="XFB1" s="4"/>
       <c r="XFC1" s="4"/>
+      <c r="XFD1" s="4"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:1024 1025:16383">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:1024 1025:16384">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
+      <c r="D2" s="4"/>
+      <c r="E2" s="3" t="s">
+        <v>7</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="F2" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -33898,20 +33936,23 @@
       <c r="XFA2" s="4"/>
       <c r="XFB2" s="4"/>
       <c r="XFC2" s="4"/>
+      <c r="XFD2" s="4"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:1024 1025:16383">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:1024 1025:16384">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -50289,92 +50330,111 @@
       <c r="XFA3" s="4"/>
       <c r="XFB3" s="4"/>
       <c r="XFC3" s="4"/>
+      <c r="XFD3" s="4"/>
     </row>
-    <row r="4" customHeight="1" spans="1:1024 1025:16383">
+    <row r="4" customHeight="1" spans="1:1024 1025:16384">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
     </row>
-    <row r="5" customHeight="1" spans="1:1024 1025:16383">
+    <row r="5" customHeight="1" spans="1:1024 1025:16384">
       <c r="A5" s="5">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2">
         <v>4011001</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="2">
+        <v>200</v>
+      </c>
     </row>
-    <row r="6" customHeight="1" spans="1:1024 1025:16383">
+    <row r="6" customHeight="1" spans="1:1024 1025:16384">
       <c r="A6" s="5">
-        <v>1002</v>
+        <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" s="2">
         <v>4011002</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>11</v>
+      <c r="E6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="2">
+        <v>200</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:1024 1025:16383">
+    <row r="7" customHeight="1" spans="1:1024 1025:16384">
       <c r="A7" s="5">
-        <v>1003</v>
+        <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2">
         <v>4011003</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>13</v>
+      <c r="E7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2">
+        <v>200</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:1024 1025:16383">
+    <row r="8" customHeight="1" spans="1:1024 1025:16384">
       <c r="A8" s="5">
-        <v>1004</v>
+        <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2">
         <v>4011004</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>15</v>
+      <c r="E8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="2">
+        <v>200</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:1024 1025:16383">
+    <row r="9" customHeight="1" spans="1:1024 1025:16384">
       <c r="A9" s="5">
-        <v>1005</v>
+        <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" s="2">
         <v>4011005</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>17</v>
+      <c r="E9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="2">
+        <v>200</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:1024 1025:16383">
+    <row r="10" customHeight="1" spans="1:1024 1025:16384">
       <c r="A10" s="5">
-        <v>1006</v>
+        <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C10" s="2">
         <v>4011006</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>19</v>
+      <c r="E10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="2">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
